--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88630</v>
+        <v>88633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125908494</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125908617</v>
+        <v>125909015</v>
       </c>
       <c r="B12" t="n">
-        <v>91224</v>
+        <v>80070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,34 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432258</v>
+        <v>432189</v>
       </c>
       <c r="R12" t="n">
-        <v>6888757</v>
+        <v>6888804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1797,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1817,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125909015</v>
+        <v>125907591</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>75066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1832,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432189</v>
+        <v>432460</v>
       </c>
       <c r="R13" t="n">
-        <v>6888804</v>
+        <v>6888186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,13 +1900,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>75066</v>
+        <v>91227</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R14" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,27 +2025,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2053,28 +2053,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R15" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,11 +2105,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2117,7 +2131,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2241,27 +2255,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B17" t="n">
-        <v>57755</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2269,32 +2283,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,21 +2331,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
         <v>125907263</v>
       </c>
       <c r="B19" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125909015</v>
+        <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,37 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432189</v>
+        <v>432258</v>
       </c>
       <c r="R12" t="n">
-        <v>6888804</v>
+        <v>6888757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,13 +1794,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1821,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125907591</v>
+        <v>125909015</v>
       </c>
       <c r="B13" t="n">
-        <v>75066</v>
+        <v>80070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,34 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432460</v>
+        <v>432189</v>
       </c>
       <c r="R13" t="n">
-        <v>6888186</v>
+        <v>6888804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1899,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125908617</v>
+        <v>125907591</v>
       </c>
       <c r="B14" t="n">
-        <v>91227</v>
+        <v>75066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432258</v>
+        <v>432460</v>
       </c>
       <c r="R14" t="n">
-        <v>6888757</v>
+        <v>6888186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B19" t="n">
-        <v>91245</v>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R19" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>91245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R20" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125906995</v>
       </c>
       <c r="B3" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>125908680</v>
       </c>
       <c r="B5" t="n">
-        <v>80036</v>
+        <v>80037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>125907032</v>
       </c>
       <c r="B6" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>125907158</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>125907155</v>
       </c>
       <c r="B8" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125909017</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125908494</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>125908684</v>
       </c>
       <c r="B11" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125909015</v>
+        <v>125907591</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>75067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1828,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432189</v>
+        <v>432460</v>
       </c>
       <c r="R13" t="n">
-        <v>6888804</v>
+        <v>6888186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,13 +1896,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125907591</v>
+        <v>125909015</v>
       </c>
       <c r="B14" t="n">
-        <v>75066</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,34 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432460</v>
+        <v>432189</v>
       </c>
       <c r="R14" t="n">
-        <v>6888186</v>
+        <v>6888804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,12 +2001,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,27 +2025,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B15" t="n">
-        <v>57755</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2053,32 +2053,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R15" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,21 +2101,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2131,7 +2117,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2152,7 +2138,7 @@
         <v>125906993</v>
       </c>
       <c r="B16" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,27 +2241,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57755</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,28 +2269,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2331,11 +2321,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
         <v>125907081</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>125907306</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>125907263</v>
       </c>
       <c r="B20" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>125907235</v>
       </c>
       <c r="B21" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125909017</v>
+        <v>125908494</v>
       </c>
       <c r="B9" t="n">
-        <v>80072</v>
+        <v>91246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,37 +1416,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432189</v>
+        <v>432276</v>
       </c>
       <c r="R9" t="n">
-        <v>6888804</v>
+        <v>6888694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,13 +1484,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1511,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125908494</v>
+        <v>125909017</v>
       </c>
       <c r="B10" t="n">
-        <v>91246</v>
+        <v>80072</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1518,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432276</v>
+        <v>432189</v>
       </c>
       <c r="R10" t="n">
-        <v>6888694</v>
+        <v>6888804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,12 +1589,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125908617</v>
+        <v>125907591</v>
       </c>
       <c r="B12" t="n">
-        <v>91228</v>
+        <v>75067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432258</v>
+        <v>432460</v>
       </c>
       <c r="R12" t="n">
-        <v>6888757</v>
+        <v>6888186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125907591</v>
+        <v>125909015</v>
       </c>
       <c r="B13" t="n">
-        <v>75067</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,34 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432460</v>
+        <v>432189</v>
       </c>
       <c r="R13" t="n">
-        <v>6888186</v>
+        <v>6888804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,12 +1899,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1919,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125909015</v>
+        <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>91228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,37 +1934,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432189</v>
+        <v>432258</v>
       </c>
       <c r="R14" t="n">
-        <v>6888804</v>
+        <v>6888757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,13 +2002,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -2025,27 +2025,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2053,28 +2053,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R15" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,11 +2105,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2117,7 +2131,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2241,27 +2255,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B17" t="n">
-        <v>57755</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2269,32 +2283,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,21 +2331,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125906995</v>
       </c>
       <c r="B3" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>125908680</v>
       </c>
       <c r="B5" t="n">
-        <v>80037</v>
+        <v>80041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>125907032</v>
       </c>
       <c r="B6" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>125907158</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>125907155</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125908494</v>
       </c>
       <c r="B9" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>125909017</v>
       </c>
       <c r="B10" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>125908684</v>
       </c>
       <c r="B11" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>125909015</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,46 +2025,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B15" t="n">
-        <v>57755</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2072,13 +2063,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R15" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,33 +2096,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2149,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125906993</v>
+        <v>125910307</v>
       </c>
       <c r="B16" t="n">
-        <v>79586</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,37 +2142,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432691</v>
+        <v>432119</v>
       </c>
       <c r="R16" t="n">
-        <v>6887698</v>
+        <v>6887838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,13 +2218,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2255,27 +2241,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57755</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,28 +2269,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2331,11 +2321,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
         <v>125907081</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>91250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R19" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B20" t="n">
-        <v>91246</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R20" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
         <v>125907235</v>
       </c>
       <c r="B21" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>75067</v>
+        <v>91232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R12" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125909015</v>
+        <v>125907591</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>75067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1828,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432189</v>
+        <v>432460</v>
       </c>
       <c r="R13" t="n">
-        <v>6888804</v>
+        <v>6888186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,13 +1896,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125908617</v>
+        <v>125909015</v>
       </c>
       <c r="B14" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,34 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432258</v>
+        <v>432189</v>
       </c>
       <c r="R14" t="n">
-        <v>6888757</v>
+        <v>6888804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,12 +2001,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125906993</v>
+        <v>125910307</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,37 +2036,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432691</v>
+        <v>432119</v>
       </c>
       <c r="R15" t="n">
-        <v>6887698</v>
+        <v>6887838</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,13 +2112,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2131,27 +2135,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2159,28 +2163,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R16" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2207,11 +2215,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2223,7 +2241,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,46 +2259,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B17" t="n">
-        <v>57755</v>
+        <v>79590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2288,13 +2297,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,33 +2330,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B19" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R19" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>91250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R20" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125910307</v>
+        <v>125906993</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,42 +2036,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432119</v>
+        <v>432691</v>
       </c>
       <c r="R15" t="n">
-        <v>6887838</v>
+        <v>6887698</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,12 +2107,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2135,27 +2131,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B16" t="n">
-        <v>57755</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2163,32 +2159,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R16" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,21 +2207,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2241,7 +2223,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2259,37 +2241,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125906993</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>57755</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2297,13 +2288,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432691</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887698</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,24 +2321,33 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125906995</v>
       </c>
       <c r="B3" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>125908680</v>
       </c>
       <c r="B5" t="n">
-        <v>80041</v>
+        <v>80042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>125907032</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>125907158</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>125907155</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125908494</v>
+        <v>125909017</v>
       </c>
       <c r="B9" t="n">
-        <v>91250</v>
+        <v>80077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,34 +1416,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432276</v>
+        <v>432189</v>
       </c>
       <c r="R9" t="n">
-        <v>6888694</v>
+        <v>6888804</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,12 +1487,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1507,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125909017</v>
+        <v>125908494</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>91252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,37 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432189</v>
+        <v>432276</v>
       </c>
       <c r="R10" t="n">
-        <v>6888804</v>
+        <v>6888694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,13 +1590,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1616,7 +1616,7 @@
         <v>125908684</v>
       </c>
       <c r="B11" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125907591</v>
+        <v>125909015</v>
       </c>
       <c r="B13" t="n">
-        <v>75067</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,34 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432460</v>
+        <v>432189</v>
       </c>
       <c r="R13" t="n">
-        <v>6888186</v>
+        <v>6888804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,12 +1899,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1919,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125909015</v>
+        <v>125907591</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>75068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,37 +1934,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432189</v>
+        <v>432460</v>
       </c>
       <c r="R14" t="n">
-        <v>6888804</v>
+        <v>6888186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,13 +2002,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,37 +2025,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125906993</v>
+        <v>125909293</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>57756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,13 +2072,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432691</v>
+        <v>432137</v>
       </c>
       <c r="R15" t="n">
-        <v>6887698</v>
+        <v>6888528</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,24 +2105,33 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2131,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125910307</v>
+        <v>125906993</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>79591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,42 +2160,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432119</v>
+        <v>432691</v>
       </c>
       <c r="R16" t="n">
-        <v>6887838</v>
+        <v>6887698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,12 +2231,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,27 +2255,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B17" t="n">
-        <v>57755</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2269,32 +2283,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,21 +2331,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
         <v>125907081</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B19" t="n">
-        <v>80075</v>
+        <v>91252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R19" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B20" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R20" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
         <v>125907235</v>
       </c>
       <c r="B21" t="n">
-        <v>77926</v>
+        <v>77927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>125908494</v>
       </c>
       <c r="B10" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125908617</v>
+        <v>125907591</v>
       </c>
       <c r="B12" t="n">
-        <v>91234</v>
+        <v>75068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432258</v>
+        <v>432460</v>
       </c>
       <c r="R12" t="n">
-        <v>6888757</v>
+        <v>6888186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>75068</v>
+        <v>91236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R14" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,46 +2025,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B15" t="n">
-        <v>57756</v>
+        <v>79591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2072,13 +2063,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R15" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,33 +2096,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2149,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125906993</v>
+        <v>125910307</v>
       </c>
       <c r="B16" t="n">
-        <v>79591</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,37 +2142,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432691</v>
+        <v>432119</v>
       </c>
       <c r="R16" t="n">
-        <v>6887698</v>
+        <v>6887838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,13 +2218,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2255,27 +2241,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,28 +2269,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2331,11 +2321,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
         <v>125907263</v>
       </c>
       <c r="B19" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B19" t="n">
-        <v>91254</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R19" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>91254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R20" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125909017</v>
+        <v>125908494</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,37 +1416,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432189</v>
+        <v>432276</v>
       </c>
       <c r="R9" t="n">
-        <v>6888804</v>
+        <v>6888694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,13 +1484,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1511,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125908494</v>
+        <v>125909017</v>
       </c>
       <c r="B10" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1518,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432276</v>
+        <v>432189</v>
       </c>
       <c r="R10" t="n">
-        <v>6888694</v>
+        <v>6888804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,12 +1589,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>75068</v>
+        <v>91238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R12" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125908617</v>
+        <v>125907591</v>
       </c>
       <c r="B14" t="n">
-        <v>91236</v>
+        <v>75068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432258</v>
+        <v>432460</v>
       </c>
       <c r="R14" t="n">
-        <v>6888757</v>
+        <v>6888186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>91256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R19" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B20" t="n">
-        <v>91254</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R20" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125906995</v>
       </c>
       <c r="B3" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>125908680</v>
       </c>
       <c r="B5" t="n">
-        <v>80042</v>
+        <v>80046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>125907032</v>
       </c>
       <c r="B6" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>125907158</v>
       </c>
       <c r="B7" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>125907155</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125908494</v>
       </c>
       <c r="B9" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>125909017</v>
       </c>
       <c r="B10" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>125908684</v>
       </c>
       <c r="B11" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125908617</v>
+        <v>125907591</v>
       </c>
       <c r="B12" t="n">
-        <v>91238</v>
+        <v>75072</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432258</v>
+        <v>432460</v>
       </c>
       <c r="R12" t="n">
-        <v>6888757</v>
+        <v>6888186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
         <v>125909015</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>75068</v>
+        <v>91242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R14" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
         <v>125906993</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>125910307</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>125907081</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907263</v>
+        <v>125907306</v>
       </c>
       <c r="B19" t="n">
-        <v>91256</v>
+        <v>80080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432534</v>
+        <v>432536</v>
       </c>
       <c r="R19" t="n">
-        <v>6888007</v>
+        <v>6888033</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907306</v>
+        <v>125907263</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>91260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432536</v>
+        <v>432534</v>
       </c>
       <c r="R20" t="n">
-        <v>6888033</v>
+        <v>6888007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
         <v>125907235</v>
       </c>
       <c r="B21" t="n">
-        <v>77927</v>
+        <v>77931</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -2025,37 +2025,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125906993</v>
+        <v>125909293</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>57760</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,13 +2072,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432691</v>
+        <v>432137</v>
       </c>
       <c r="R15" t="n">
-        <v>6887698</v>
+        <v>6888528</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,24 +2105,33 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2131,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125910307</v>
+        <v>125906993</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>79595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,42 +2160,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432119</v>
+        <v>432691</v>
       </c>
       <c r="R16" t="n">
-        <v>6887838</v>
+        <v>6887698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,12 +2231,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,27 +2255,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B17" t="n">
-        <v>57760</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2269,32 +2283,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,21 +2331,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125908494</v>
+        <v>125909017</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,34 +1416,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432276</v>
+        <v>432189</v>
       </c>
       <c r="R9" t="n">
-        <v>6888694</v>
+        <v>6888804</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,12 +1487,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1507,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125909017</v>
+        <v>125908494</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,37 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432189</v>
+        <v>432276</v>
       </c>
       <c r="R10" t="n">
-        <v>6888804</v>
+        <v>6888694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,13 +1590,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>75072</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R12" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125909015</v>
+        <v>125907591</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>75072</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1828,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432189</v>
+        <v>432460</v>
       </c>
       <c r="R13" t="n">
-        <v>6888804</v>
+        <v>6888186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,13 +1896,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125908617</v>
+        <v>125909015</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,34 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432258</v>
+        <v>432189</v>
       </c>
       <c r="R14" t="n">
-        <v>6888757</v>
+        <v>6888804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,12 +2001,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,46 +2025,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B15" t="n">
-        <v>57760</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2072,13 +2063,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R15" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2105,33 +2096,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2149,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125906993</v>
+        <v>125910307</v>
       </c>
       <c r="B16" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,37 +2142,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432691</v>
+        <v>432119</v>
       </c>
       <c r="R16" t="n">
-        <v>6887698</v>
+        <v>6887838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,13 +2218,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2255,27 +2241,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,28 +2269,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2331,11 +2321,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -2131,27 +2131,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57760</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2159,28 +2159,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R16" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2207,11 +2211,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2223,7 +2237,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,27 +2255,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B17" t="n">
-        <v>57760</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2269,32 +2283,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,21 +2331,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125909017</v>
+        <v>125908494</v>
       </c>
       <c r="B9" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,37 +1416,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432189</v>
+        <v>432276</v>
       </c>
       <c r="R9" t="n">
-        <v>6888804</v>
+        <v>6888694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,13 +1484,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1511,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125908494</v>
+        <v>125909017</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1518,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432276</v>
+        <v>432189</v>
       </c>
       <c r="R10" t="n">
-        <v>6888694</v>
+        <v>6888804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,12 +1589,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125908617</v>
+        <v>125909015</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,34 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432258</v>
+        <v>432189</v>
       </c>
       <c r="R12" t="n">
-        <v>6888757</v>
+        <v>6888804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1797,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1919,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125909015</v>
+        <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,37 +1934,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432189</v>
+        <v>432258</v>
       </c>
       <c r="R14" t="n">
-        <v>6888804</v>
+        <v>6888757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,13 +2002,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2131,27 +2131,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125909293</v>
+        <v>125910307</v>
       </c>
       <c r="B16" t="n">
-        <v>57760</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2159,32 +2159,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432137</v>
+        <v>432119</v>
       </c>
       <c r="R16" t="n">
-        <v>6888528</v>
+        <v>6887838</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2211,21 +2207,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2237,7 +2223,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2255,27 +2241,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,28 +2269,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2331,11 +2321,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125909015</v>
+        <v>125908617</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,37 +1726,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432189</v>
+        <v>432258</v>
       </c>
       <c r="R12" t="n">
-        <v>6888804</v>
+        <v>6888757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,13 +1794,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1821,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125907591</v>
+        <v>125909015</v>
       </c>
       <c r="B13" t="n">
-        <v>75072</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,34 +1828,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432460</v>
+        <v>432189</v>
       </c>
       <c r="R13" t="n">
-        <v>6888186</v>
+        <v>6888804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1899,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125908617</v>
+        <v>125907591</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>75072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432258</v>
+        <v>432460</v>
       </c>
       <c r="R14" t="n">
-        <v>6888757</v>
+        <v>6888186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125906993</v>
+        <v>125910307</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,37 +2036,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432691</v>
+        <v>432119</v>
       </c>
       <c r="R15" t="n">
-        <v>6887698</v>
+        <v>6887838</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,13 +2112,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2131,27 +2135,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57760</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2159,28 +2163,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R16" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2207,11 +2215,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2223,7 +2241,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,46 +2259,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B17" t="n">
-        <v>57760</v>
+        <v>79595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2288,13 +2297,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,33 +2330,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125907611</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125906995</v>
       </c>
       <c r="B3" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>125908416</v>
       </c>
       <c r="B4" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>125908680</v>
       </c>
       <c r="B5" t="n">
-        <v>80046</v>
+        <v>80049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>125907032</v>
       </c>
       <c r="B6" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>125907158</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>125907155</v>
       </c>
       <c r="B8" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>125908494</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>125909017</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>125908684</v>
       </c>
       <c r="B11" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125908617</v>
+        <v>125909015</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,34 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432258</v>
+        <v>432189</v>
       </c>
       <c r="R12" t="n">
-        <v>6888757</v>
+        <v>6888804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1797,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1817,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125909015</v>
+        <v>125907591</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>75075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,37 +1832,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432189</v>
+        <v>432460</v>
       </c>
       <c r="R13" t="n">
-        <v>6888804</v>
+        <v>6888186</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,13 +1900,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125907591</v>
+        <v>125908617</v>
       </c>
       <c r="B14" t="n">
-        <v>75072</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432460</v>
+        <v>432258</v>
       </c>
       <c r="R14" t="n">
-        <v>6888186</v>
+        <v>6888757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
         <v>125910307</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,46 +2135,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B16" t="n">
-        <v>57760</v>
+        <v>79598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2182,13 +2173,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R16" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,33 +2206,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2259,37 +2241,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125906993</v>
+        <v>125909293</v>
       </c>
       <c r="B17" t="n">
-        <v>79595</v>
+        <v>57761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2297,13 +2288,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432691</v>
+        <v>432137</v>
       </c>
       <c r="R17" t="n">
-        <v>6887698</v>
+        <v>6888528</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,24 +2321,33 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
         <v>125907081</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>125907306</v>
       </c>
       <c r="B19" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>125907263</v>
       </c>
       <c r="B20" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>125907235</v>
       </c>
       <c r="B21" t="n">
-        <v>77931</v>
+        <v>77934</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -2135,37 +2135,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125906993</v>
+        <v>125909293</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>57761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2173,13 +2182,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432691</v>
+        <v>432137</v>
       </c>
       <c r="R16" t="n">
-        <v>6887698</v>
+        <v>6888528</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2206,24 +2215,33 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2241,46 +2259,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125909293</v>
+        <v>125906993</v>
       </c>
       <c r="B17" t="n">
-        <v>57761</v>
+        <v>79598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2288,13 +2297,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432137</v>
+        <v>432691</v>
       </c>
       <c r="R17" t="n">
-        <v>6888528</v>
+        <v>6887698</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,33 +2330,24 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125907611</v>
+        <v>125906995</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432449</v>
+        <v>432691</v>
       </c>
       <c r="R2" t="n">
-        <v>6888182</v>
+        <v>6887698</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +757,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125906995</v>
+        <v>125908416</v>
       </c>
       <c r="B3" t="n">
-        <v>78647</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432691</v>
+        <v>432246</v>
       </c>
       <c r="R3" t="n">
-        <v>6887698</v>
+        <v>6888694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,13 +860,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125908416</v>
+        <v>125908617</v>
       </c>
       <c r="B4" t="n">
-        <v>88654</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432246</v>
+        <v>432258</v>
       </c>
       <c r="R4" t="n">
-        <v>6888694</v>
+        <v>6888757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,45 +985,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125908680</v>
+        <v>125909017</v>
       </c>
       <c r="B5" t="n">
-        <v>80049</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432299</v>
+        <v>432189</v>
       </c>
       <c r="R5" t="n">
-        <v>6888739</v>
+        <v>6888804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,12 +1067,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles, lågproduktiv grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1087,48 +1091,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125907032</v>
+        <v>125907081</v>
       </c>
       <c r="B6" t="n">
-        <v>79569</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432724</v>
+        <v>432720</v>
       </c>
       <c r="R6" t="n">
-        <v>6887824</v>
+        <v>6887891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,13 +1170,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125907158</v>
+        <v>125910412</v>
       </c>
       <c r="B7" t="n">
-        <v>78739</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,21 +1204,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432644</v>
+        <v>432065</v>
       </c>
       <c r="R7" t="n">
-        <v>6887961</v>
+        <v>6887836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Barrnaturskog i exponerat högläge</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125907155</v>
+        <v>125907591</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,37 +1310,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432644</v>
+        <v>432460</v>
       </c>
       <c r="R8" t="n">
-        <v>6887961</v>
+        <v>6888186</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,13 +1378,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1405,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125908494</v>
+        <v>125907155</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,34 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432276</v>
+        <v>432644</v>
       </c>
       <c r="R9" t="n">
-        <v>6888694</v>
+        <v>6887961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,12 +1483,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125909017</v>
+        <v>125906993</v>
       </c>
       <c r="B10" t="n">
-        <v>80084</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432189</v>
+        <v>432691</v>
       </c>
       <c r="R10" t="n">
-        <v>6888804</v>
+        <v>6887698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1613,32 +1613,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125908684</v>
+        <v>125907306</v>
       </c>
       <c r="B11" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432299</v>
+        <v>432536</v>
       </c>
       <c r="R11" t="n">
-        <v>6888739</v>
+        <v>6888033</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
         <v>125909015</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,32 +1821,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125907591</v>
+        <v>125908684</v>
       </c>
       <c r="B13" t="n">
-        <v>75075</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432460</v>
+        <v>432299</v>
       </c>
       <c r="R13" t="n">
-        <v>6888186</v>
+        <v>6888739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125908617</v>
+        <v>125910307</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,34 +1934,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hålåsen, Hålåsen, Hjd</t>
+          <t>Hålåsen, Linsell, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432258</v>
+        <v>432119</v>
       </c>
       <c r="R14" t="n">
-        <v>6888757</v>
+        <v>6887838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2015,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2025,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125910307</v>
+        <v>125909293</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,16 +2044,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2053,28 +2061,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hålåsen, Linsell, Hjd</t>
+          <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432119</v>
+        <v>432137</v>
       </c>
       <c r="R15" t="n">
-        <v>6887838</v>
+        <v>6888528</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,11 +2113,21 @@
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2117,7 +2139,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Grannaturskog i bäckdråg</t>
+          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2135,60 +2157,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125909293</v>
+        <v>125910346</v>
       </c>
       <c r="B16" t="n">
-        <v>57761</v>
+        <v>101897</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>220075</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432137</v>
+        <v>432093</v>
       </c>
       <c r="R16" t="n">
-        <v>6888528</v>
+        <v>6887834</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,21 +2225,11 @@
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gles, lågproduktiv och hänglavsrik grannaturskog i högläge</t>
+          <t>Grannaturskog i bäckdråg</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2259,48 +2259,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125906993</v>
+        <v>125907611</v>
       </c>
       <c r="B17" t="n">
-        <v>79598</v>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432691</v>
+        <v>432449</v>
       </c>
       <c r="R17" t="n">
-        <v>6887698</v>
+        <v>6888182</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,13 +2338,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
+          <t>Gammal grannaturskog i högläge</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2365,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125907081</v>
+        <v>125907235</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>78339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2376,21 +2372,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2400,10 +2396,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432720</v>
+        <v>432607</v>
       </c>
       <c r="R18" t="n">
-        <v>6887891</v>
+        <v>6887975</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125907306</v>
+        <v>125907158</v>
       </c>
       <c r="B19" t="n">
-        <v>80083</v>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,34 +2474,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432536</v>
+        <v>432644</v>
       </c>
       <c r="R19" t="n">
-        <v>6888033</v>
+        <v>6887961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,12 +2545,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2569,32 +2569,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125907263</v>
+        <v>125908680</v>
       </c>
       <c r="B20" t="n">
-        <v>91263</v>
+        <v>80398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432534</v>
+        <v>432299</v>
       </c>
       <c r="R20" t="n">
-        <v>6888007</v>
+        <v>6888739</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Bördig grannaturskog med ett fältskikt av midsommarblomster, ekbräken och harsyra.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125907235</v>
+        <v>125907032</v>
       </c>
       <c r="B21" t="n">
-        <v>77934</v>
+        <v>79917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,34 +2682,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hålåsen, Hålåsen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432607</v>
+        <v>432724</v>
       </c>
       <c r="R21" t="n">
-        <v>6887975</v>
+        <v>6887824</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,12 +2753,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Gammal grannaturskog i högläge</t>
+          <t>Gles tallskog, delvis på hällmärk, med relativt goda mängder silverved och brandstubbar</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>

--- a/artfynd/A 1242-2025 artfynd.xlsx
+++ b/artfynd/A 1242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125906995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908416</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907081</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125910412</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907591</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907155</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125906993</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907306</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909015</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908684</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125910307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2154,6 +2224,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125909293</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2256,6 +2331,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125910346</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907611</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2460,6 +2545,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907235</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907158</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908680</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,8 +2874,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125907032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>